--- a/data/trans_dic/P19C04-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19C04-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por la extracción de algún diente o muela</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por la extracción de algún diente o muela (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,72; 34,64</t>
+          <t>27,64; 34,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37,78; 45,07</t>
+          <t>37,85; 45,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29,16; 37,85</t>
+          <t>28,91; 37,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30,51; 37,85</t>
+          <t>30,39; 37,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,46; 25,45</t>
+          <t>20,0; 25,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,13; 29,23</t>
+          <t>24,0; 29,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,4; 25,36</t>
+          <t>18,53; 25,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,28; 25,88</t>
+          <t>21,16; 25,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,07; 28,31</t>
+          <t>24,04; 28,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,43; 35,09</t>
+          <t>30,42; 34,94</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23,76; 29,31</t>
+          <t>23,86; 29,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,56; 29,5</t>
+          <t>25,69; 30,05</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,27; 20,57</t>
+          <t>16,1; 20,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,99; 22,93</t>
+          <t>18,96; 22,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,48; 18,18</t>
+          <t>14,56; 18,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,44; 14,16</t>
+          <t>8,46; 14,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,94; 13,39</t>
+          <t>9,96; 13,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,09; 15,57</t>
+          <t>12,02; 15,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,02; 13,22</t>
+          <t>9,85; 12,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,74; 9,4</t>
+          <t>5,7; 9,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,42; 16,1</t>
+          <t>13,57; 16,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,21; 18,93</t>
+          <t>16,01; 18,92</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12,74; 15,2</t>
+          <t>12,69; 15,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,16; 11,54</t>
+          <t>8,03; 11,44</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,66; 11,23</t>
+          <t>5,87; 11,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,37; 13,84</t>
+          <t>7,5; 13,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,11; 11,75</t>
+          <t>6,38; 11,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,14; 10,88</t>
+          <t>6,13; 10,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,11; 9,05</t>
+          <t>4,17; 8,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,45; 11,11</t>
+          <t>5,33; 11,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,56; 10,49</t>
+          <t>5,46; 10,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 6,43</t>
+          <t>3,53; 6,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,45; 9,24</t>
+          <t>5,63; 9,15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,09; 11,52</t>
+          <t>7,06; 11,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,55; 10,01</t>
+          <t>6,64; 10,04</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,19; 7,91</t>
+          <t>5,18; 7,69</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,37; 21,65</t>
+          <t>18,3; 21,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,09; 26,42</t>
+          <t>23,1; 26,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,36; 19,33</t>
+          <t>16,35; 19,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,36; 16,38</t>
+          <t>11,37; 16,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,28; 15,96</t>
+          <t>13,46; 16,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,09; 18,94</t>
+          <t>16,09; 18,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,81; 14,53</t>
+          <t>11,88; 14,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,57; 11,69</t>
+          <t>8,64; 11,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,06; 18,26</t>
+          <t>16,14; 18,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,98; 22,14</t>
+          <t>19,91; 22,11</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,22; 16,28</t>
+          <t>14,39; 16,42</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,7; 13,55</t>
+          <t>10,79; 13,46</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por la extracción de algún diente o muela</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por la extracción de algún diente o muela (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>191114; 238782</t>
+          <t>190569; 238703</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>294393; 351183</t>
+          <t>294941; 351186</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>133399; 173138</t>
+          <t>132234; 173713</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>147478; 182958</t>
+          <t>146893; 183175</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>196204; 244097</t>
+          <t>191833; 242784</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>272242; 329800</t>
+          <t>270729; 331101</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>117552; 162029</t>
+          <t>118384; 161901</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>153524; 186770</t>
+          <t>152704; 186093</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>396815; 466579</t>
+          <t>396259; 466695</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>580470; 669275</t>
+          <t>580232; 666416</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>260470; 321290</t>
+          <t>261610; 319962</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>308017; 355498</t>
+          <t>309504; 362136</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>213805; 270349</t>
+          <t>211668; 266966</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>320674; 387149</t>
+          <t>320112; 387949</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>245629; 308415</t>
+          <t>247100; 309980</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>188357; 315787</t>
+          <t>188668; 316331</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>136546; 183822</t>
+          <t>136780; 183238</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>192103; 247503</t>
+          <t>190975; 246094</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>171104; 225800</t>
+          <t>168121; 221741</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>126127; 206587</t>
+          <t>125189; 208016</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>360806; 432678</t>
+          <t>364787; 439060</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>531226; 620495</t>
+          <t>524840; 619991</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>433741; 517462</t>
+          <t>432136; 510766</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>361189; 510862</t>
+          <t>355446; 506724</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>25505; 50623</t>
+          <t>26478; 50849</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32571; 61174</t>
+          <t>33160; 61285</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30501; 58675</t>
+          <t>31829; 59081</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38746; 68716</t>
+          <t>38689; 66931</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16791; 36998</t>
+          <t>17048; 36754</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23095; 47088</t>
+          <t>22588; 47755</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28250; 53298</t>
+          <t>27760; 52583</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22200; 41901</t>
+          <t>22985; 42133</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46896; 79408</t>
+          <t>48368; 78622</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>61380; 99740</t>
+          <t>61163; 96587</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65974; 100866</t>
+          <t>66888; 101166</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>66562; 101460</t>
+          <t>66418; 98631</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>450878; 531386</t>
+          <t>449175; 530224</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>671870; 768829</t>
+          <t>672222; 767242</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>434063; 512854</t>
+          <t>433711; 514123</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>380117; 547821</t>
+          <t>380265; 541993</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>364094; 437561</t>
+          <t>368865; 439813</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>505517; 595047</t>
+          <t>505336; 593276</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>337117; 414753</t>
+          <t>339029; 412680</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>305975; 417478</t>
+          <t>308413; 415762</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>834415; 948895</t>
+          <t>838333; 946159</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1209006; 1339380</t>
+          <t>1204904; 1337668</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>783047; 896637</t>
+          <t>792823; 904652</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>740069; 936856</t>
+          <t>746200; 930891</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C04-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19C04-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,64; 34,63</t>
+          <t>27,56; 34,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37,85; 45,07</t>
+          <t>37,92; 45,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,91; 37,98</t>
+          <t>28,92; 37,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30,39; 37,9</t>
+          <t>30,81; 38,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,0; 25,32</t>
+          <t>20,17; 25,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,0; 29,35</t>
+          <t>23,93; 29,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,53; 25,34</t>
+          <t>18,53; 25,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,16; 25,79</t>
+          <t>20,97; 25,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,04; 28,31</t>
+          <t>24,03; 28,35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,42; 34,94</t>
+          <t>30,6; 34,86</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23,86; 29,19</t>
+          <t>23,75; 29,22</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,69; 30,05</t>
+          <t>25,56; 29,87</t>
         </is>
       </c>
     </row>
@@ -804,47 +804,47 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>14,56%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>11,61%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>13,74%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>11,43%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>9,49%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>14,84%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>17,4%</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>13,85%</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
           <t>12,04%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>11,61%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>13,74%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,43%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>7,99%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>14,84%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>17,4%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>13,85%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,1; 20,31</t>
+          <t>16,18; 20,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,96; 22,98</t>
+          <t>19,06; 22,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,56; 18,27</t>
+          <t>14,64; 18,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,46; 14,18</t>
+          <t>12,97; 16,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,96; 13,34</t>
+          <t>10,14; 13,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,02; 15,49</t>
+          <t>11,99; 15,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,85; 12,99</t>
+          <t>9,84; 13,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,7; 9,46</t>
+          <t>8,38; 10,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,57; 16,34</t>
+          <t>13,57; 16,31</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,01; 18,92</t>
+          <t>16,09; 18,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12,69; 15,0</t>
+          <t>12,56; 15,11</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,03; 11,44</t>
+          <t>11,05; 13,0</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,87; 11,28</t>
+          <t>5,95; 11,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,5; 13,86</t>
+          <t>7,51; 13,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,38; 11,83</t>
+          <t>6,48; 11,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,13; 10,6</t>
+          <t>6,28; 10,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,17; 8,99</t>
+          <t>4,14; 8,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,33; 11,27</t>
+          <t>5,15; 10,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,46; 10,34</t>
+          <t>5,4; 10,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 6,47</t>
+          <t>3,49; 6,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,63; 9,15</t>
+          <t>5,59; 9,29</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,06; 11,16</t>
+          <t>6,96; 11,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,64; 10,04</t>
+          <t>6,57; 10,14</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,18; 7,69</t>
+          <t>5,35; 7,9</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,3; 21,6</t>
+          <t>18,43; 21,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,1; 26,37</t>
+          <t>23,03; 26,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,35; 19,38</t>
+          <t>16,29; 19,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,37; 16,2</t>
+          <t>15,24; 17,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,46; 16,05</t>
+          <t>13,43; 16,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,09; 18,89</t>
+          <t>16,15; 18,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,88; 14,46</t>
+          <t>11,73; 14,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,64; 11,64</t>
+          <t>10,67; 12,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,14; 18,21</t>
+          <t>16,14; 18,29</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,91; 22,11</t>
+          <t>19,95; 22,07</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,39; 16,42</t>
+          <t>14,35; 16,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,79; 13,46</t>
+          <t>13,02; 14,65</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>164796</t>
+          <t>184581</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>169076</t>
+          <t>181440</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>333872</t>
+          <t>366021</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>190569; 238703</t>
+          <t>190023; 236563</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>294941; 351186</t>
+          <t>295466; 353325</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>132234; 173713</t>
+          <t>132301; 172466</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>146893; 183175</t>
+          <t>165155; 206047</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>191833; 242784</t>
+          <t>193383; 245687</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>270729; 331101</t>
+          <t>269993; 329853</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>118384; 161901</t>
+          <t>118378; 162410</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>152704; 186093</t>
+          <t>164520; 201446</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>396259; 466695</t>
+          <t>396064; 467357</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>580232; 666416</t>
+          <t>583694; 664907</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>261610; 319962</t>
+          <t>260377; 320388</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>309504; 362136</t>
+          <t>337624; 394461</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>268600</t>
+          <t>312511</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>175652</t>
+          <t>200250</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>444252</t>
+          <t>512761</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>211668; 266966</t>
+          <t>212645; 267846</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>320112; 387949</t>
+          <t>321724; 388091</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>247100; 309980</t>
+          <t>248437; 308136</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>188668; 316331</t>
+          <t>278407; 350254</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>136780; 183238</t>
+          <t>139175; 186614</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>190975; 246094</t>
+          <t>190561; 244872</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>168121; 221741</t>
+          <t>168099; 223884</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>125189; 208016</t>
+          <t>176827; 222924</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>364787; 439060</t>
+          <t>364685; 438369</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>524840; 619991</t>
+          <t>527338; 614140</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>432136; 510766</t>
+          <t>427448; 514279</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>355446; 506724</t>
+          <t>470197; 553553</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50397</t>
+          <t>57532</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31084</t>
+          <t>34756</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>81481</t>
+          <t>92288</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>26478; 50849</t>
+          <t>26810; 52333</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>33160; 61285</t>
+          <t>33199; 60783</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31829; 59081</t>
+          <t>32350; 58129</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38689; 66931</t>
+          <t>44049; 76703</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17048; 36754</t>
+          <t>16933; 36563</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22588; 47755</t>
+          <t>21815; 45194</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27760; 52583</t>
+          <t>27456; 52269</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22985; 42133</t>
+          <t>25311; 46356</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>48368; 78622</t>
+          <t>48086; 79896</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>61163; 96587</t>
+          <t>60288; 96853</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66888; 101166</t>
+          <t>66156; 102120</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>66418; 98631</t>
+          <t>76277; 112632</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>483793</t>
+          <t>554623</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>375812</t>
+          <t>416447</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>859605</t>
+          <t>971070</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>449175; 530224</t>
+          <t>452315; 532460</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>672222; 767242</t>
+          <t>669936; 766627</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>433711; 514123</t>
+          <t>432305; 511629</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>380265; 541993</t>
+          <t>515844; 598659</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>368865; 439813</t>
+          <t>368079; 443924</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>505336; 593276</t>
+          <t>507260; 592001</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>339029; 412680</t>
+          <t>334851; 413501</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>308413; 415762</t>
+          <t>386214; 451403</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>838333; 946159</t>
+          <t>838459; 950149</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1204904; 1337668</t>
+          <t>1207381; 1335356</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>792823; 904652</t>
+          <t>790354; 899902</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>746200; 930891</t>
+          <t>912108; 1025739</t>
         </is>
       </c>
     </row>
